--- a/artfynd/A 44601-2021 artfynd.xlsx
+++ b/artfynd/A 44601-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 44601-2021 artfynd.xlsx
+++ b/artfynd/A 44601-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>56218786</v>
+        <v>56218785</v>
       </c>
       <c r="B2" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>534021.8595013664</v>
+        <v>533842</v>
       </c>
       <c r="R2" t="n">
-        <v>7045223.114539093</v>
+        <v>7045356</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2013-11-05</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2013-11-05</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>56218788</v>
+        <v>56218786</v>
       </c>
       <c r="B3" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>534091.5813816639</v>
+        <v>534022</v>
       </c>
       <c r="R3" t="n">
-        <v>7045261.781453439</v>
+        <v>7045223</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,19 +844,9 @@
           <t>2013-11-05</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2013-11-05</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -910,12 +880,7 @@
         <v>56218787</v>
       </c>
       <c r="B4" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -947,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>534027.6662840721</v>
+        <v>534028</v>
       </c>
       <c r="R4" t="n">
-        <v>7045223.176621826</v>
+        <v>7045223</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,19 +945,9 @@
           <t>2013-11-05</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2013-11-05</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,122 +971,6 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>56218785</v>
-      </c>
-      <c r="B5" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>NV om Tannsjön, Jmt</t>
-        </is>
-      </c>
-      <c r="Q5" t="n">
-        <v>533842.2032871756</v>
-      </c>
-      <c r="R5" t="n">
-        <v>7045355.927142077</v>
-      </c>
-      <c r="S5" t="n">
-        <v>10</v>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>Hammerdal</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2013-11-05</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>2013-11-05</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>Sebastian Acker</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>Sebastian Acker</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
         <is>
           <t>SCA Skog Naturvärdesinventering</t>
         </is>

--- a/artfynd/A 44601-2021 artfynd.xlsx
+++ b/artfynd/A 44601-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56218785</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56218786</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,8 +990,18 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56218787</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>